--- a/設定ファイル/シリアル_48us/シリアル_48us_CLK5.xlsx
+++ b/設定ファイル/シリアル_48us/シリアル_48us_CLK5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e12206\GitHub\DCDC_clock_simulator\設定ファイル\シリアル_48us\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40373998-17EB-413E-9BEE-FC1BBC43FC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F99964B-9C57-4292-9B38-4BA4F4E2C11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4150" yWindow="0" windowWidth="14550" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>parameter</t>
   </si>
@@ -125,30 +125,6 @@
     <t>power_net_delay_ns_7</t>
   </si>
   <si>
-    <t>power_net_duty_percent_0</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_1</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_2</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_3</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_4</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_5</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_6</t>
-  </si>
-  <si>
-    <t>power_net_duty_percent_7</t>
-  </si>
-  <si>
     <t>gate_period_us</t>
   </si>
   <si>
@@ -168,6 +144,62 @@
   </si>
   <si>
     <t>clock_frequency_MHz</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_0_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_1_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_2_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_3_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_4_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_5_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_6_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_7_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_0_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_1_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_2_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_3_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_4_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_5_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_6_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_7_max</t>
   </si>
 </sst>
 </file>
@@ -533,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -703,122 +735,186 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>72.5</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>80.599999999999994</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>78.099999999999994</v>
+        <v>39.049999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>70.599999999999994</v>
+        <v>35.299999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>77.3</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>23.7</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B28" s="2">
-        <v>21</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2">
-        <v>48</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B30" s="2">
-        <v>0.64</v>
+        <v>80.599999999999994</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2">
-        <v>18.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B32" s="2">
-        <v>32.799999999999997</v>
+        <v>78.099999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B33" s="2">
-        <v>47.2</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B34" s="2">
-        <v>84</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B35" s="2">
-        <f>ROUND(175/B34,2)</f>
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="2">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="2">
+        <v>32.799999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="2">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="2">
+        <f>ROUND(175/B42,2)</f>
         <v>2.08</v>
       </c>
     </row>

--- a/設定ファイル/シリアル_48us/シリアル_48us_CLK5.xlsx
+++ b/設定ファイル/シリアル_48us/シリアル_48us_CLK5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e12206\GitHub\DCDC_clock_simulator\設定ファイル\シリアル_48us\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F99964B-9C57-4292-9B38-4BA4F4E2C11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5F4410-978E-493B-9E57-2A327B52220D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4150" yWindow="0" windowWidth="14550" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
@@ -738,7 +738,7 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>36.25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -746,7 +746,7 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>40.299999999999997</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -754,7 +754,7 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -762,7 +762,7 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>39.049999999999997</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -770,7 +770,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>35.299999999999997</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -778,7 +778,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>38.65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -786,7 +786,7 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>11.85</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -794,7 +794,7 @@
         <v>44</v>
       </c>
       <c r="B28" s="2">
-        <v>10.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -802,7 +802,7 @@
         <v>45</v>
       </c>
       <c r="B29" s="2">
-        <v>72.5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -810,7 +810,7 @@
         <v>46</v>
       </c>
       <c r="B30" s="2">
-        <v>80.599999999999994</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -818,7 +818,7 @@
         <v>47</v>
       </c>
       <c r="B31" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -826,7 +826,7 @@
         <v>48</v>
       </c>
       <c r="B32" s="2">
-        <v>78.099999999999994</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -834,7 +834,7 @@
         <v>49</v>
       </c>
       <c r="B33" s="2">
-        <v>70.599999999999994</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -842,7 +842,7 @@
         <v>50</v>
       </c>
       <c r="B34" s="2">
-        <v>77.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -850,7 +850,7 @@
         <v>51</v>
       </c>
       <c r="B35" s="2">
-        <v>23.7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
